--- a/data/trans_dic/P55$auxiliar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$auxiliar-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 33,79</t>
+          <t>5,98; 33,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 33,28</t>
+          <t>6,04; 33,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 37,54</t>
+          <t>17,71; 38,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,42; 37,1</t>
+          <t>14,56; 38,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 20,49</t>
+          <t>3,77; 19,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,54; 39,83</t>
+          <t>26,12; 39,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>0,0; 6,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,93; 30,06</t>
+          <t>13,69; 31,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 20,16</t>
+          <t>6,65; 21,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,02; 36,82</t>
+          <t>24,5; 36,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 22,24</t>
+          <t>2,47; 22,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,85; 30,59</t>
+          <t>11,41; 31,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>0,0; 7,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 25,59</t>
+          <t>8,72; 25,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,19</t>
+          <t>1,57; 13,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,36; 33,97</t>
+          <t>20,64; 34,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 21,99</t>
+          <t>8,42; 21,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 8,67</t>
+          <t>1,01; 8,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 30,1</t>
+          <t>19,22; 30,46</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,9</t>
+          <t>0,0; 16,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,06</t>
+          <t>0,0; 20,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 32,25</t>
+          <t>5,78; 33,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,45</t>
+          <t>0,0; 12,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 28,98</t>
+          <t>6,43; 27,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 21,27</t>
+          <t>2,0; 21,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,07; 28,81</t>
+          <t>12,53; 28,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,32</t>
+          <t>0,0; 8,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 20,86</t>
+          <t>6,12; 20,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,05</t>
+          <t>1,68; 15,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,58; 25,83</t>
+          <t>12,59; 25,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,71</t>
+          <t>0,0; 18,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,89</t>
+          <t>0,0; 14,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 17,35</t>
+          <t>3,86; 17,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 18,37</t>
+          <t>3,91; 18,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,16; 26,49</t>
+          <t>10,32; 26,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,89</t>
+          <t>1,56; 13,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,0; 25,81</t>
+          <t>14,27; 25,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 14,25</t>
+          <t>3,33; 15,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 19,3</t>
+          <t>7,01; 19,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,51</t>
+          <t>1,15; 9,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 21,22</t>
+          <t>12,2; 20,87</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,05</t>
+          <t>4,21; 13,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,95</t>
+          <t>2,01; 9,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,98; 23,76</t>
+          <t>14,04; 24,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,42</t>
+          <t>1,91; 7,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,99; 23,53</t>
+          <t>14,12; 23,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,54</t>
+          <t>3,81; 10,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,26; 28,07</t>
+          <t>21,19; 28,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,47</t>
+          <t>1,51; 5,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,65; 19,03</t>
+          <t>11,57; 18,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,25</t>
+          <t>3,7; 8,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,86; 25,56</t>
+          <t>19,87; 25,45</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1748</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1999; 10994</t>
+          <t>1947; 10968</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1785; 9243</t>
+          <t>1679; 9246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8756; 18627</t>
+          <t>8790; 18982</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5247</t>
+          <t>0; 5274</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9405; 22632</t>
+          <t>8884; 23240</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2285; 12321</t>
+          <t>2268; 11919</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21148; 31734</t>
+          <t>20814; 31247</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5851</t>
+          <t>0; 5329</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13030; 28120</t>
+          <t>12808; 29685</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6034; 17720</t>
+          <t>5846; 18672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32350; 47608</t>
+          <t>31681; 46955</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1837</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1117; 10155</t>
+          <t>1127; 10120</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1664</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4199; 11835</t>
+          <t>4413; 12247</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5067</t>
+          <t>0; 5365</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7761; 22604</t>
+          <t>7699; 22504</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 10133</t>
+          <t>1206; 10401</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17508; 29213</t>
+          <t>17749; 29485</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5524</t>
+          <t>0; 5438</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11998; 29463</t>
+          <t>11276; 28160</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1190; 10206</t>
+          <t>1191; 9855</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23988; 37531</t>
+          <t>23970; 37976</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1864</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5560</t>
+          <t>0; 4651</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4201</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1418; 8234</t>
+          <t>1475; 8537</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6249</t>
+          <t>0; 5616</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4096; 15046</t>
+          <t>3341; 14163</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1046; 10968</t>
+          <t>1031; 11073</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7620; 16798</t>
+          <t>7309; 16589</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4981</t>
+          <t>0; 5786</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4417; 16659</t>
+          <t>4887; 16727</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1312; 12010</t>
+          <t>1260; 11646</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10546; 21652</t>
+          <t>10552; 21134</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4322</t>
+          <t>0; 4231</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5563</t>
+          <t>0; 5780</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1656</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1383; 7501</t>
+          <t>1667; 7686</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2281; 13226</t>
+          <t>2815; 13225</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7167; 20737</t>
+          <t>8081; 20823</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1220; 10162</t>
+          <t>1231; 10288</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14602; 26908</t>
+          <t>14882; 27033</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2935; 13550</t>
+          <t>3168; 14308</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8493; 22836</t>
+          <t>8297; 23363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 9213</t>
+          <t>1241; 10130</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18007; 31294</t>
+          <t>17990; 30779</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>0; 4547</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6250; 20530</t>
+          <t>6158; 20445</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2529; 12082</t>
+          <t>2442; 11524</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21961; 37320</t>
+          <t>22056; 37927</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4324; 17142</t>
+          <t>4420; 17722</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39099; 65787</t>
+          <t>39457; 67023</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10079; 28185</t>
+          <t>10177; 29027</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>69791; 92136</t>
+          <t>69568; 92229</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5776; 19551</t>
+          <t>5392; 19014</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49579; 81000</t>
+          <t>49252; 79016</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15005; 35978</t>
+          <t>14368; 33654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96364; 124046</t>
+          <t>96424; 123491</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$auxiliar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$auxiliar-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 33,71</t>
+          <t>6,18; 33,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 33,28</t>
+          <t>8,57; 33,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 38,25</t>
+          <t>16,41; 36,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,78</t>
+          <t>0,0; 11,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 38,1</t>
+          <t>14,2; 37,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 19,82</t>
+          <t>3,77; 21,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,12; 39,22</t>
+          <t>26,28; 39,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,78</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 31,74</t>
+          <t>14,13; 31,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 21,24</t>
+          <t>6,58; 21,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 36,32</t>
+          <t>24,54; 36,15</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 22,17</t>
+          <t>2,41; 20,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,41; 31,65</t>
+          <t>10,89; 30,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,93</t>
+          <t>0,0; 7,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 25,47</t>
+          <t>9,76; 24,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 13,54</t>
+          <t>1,57; 13,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,64; 34,29</t>
+          <t>19,85; 32,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 21,02</t>
+          <t>8,98; 21,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 8,37</t>
+          <t>1,01; 8,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,22; 30,46</t>
+          <t>18,22; 29,5</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,65</t>
+          <t>0,0; 20,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,76</t>
+          <t>0,0; 17,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 33,44</t>
+          <t>5,24; 30,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,09</t>
+          <t>0,0; 13,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 27,28</t>
+          <t>7,9; 29,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 21,47</t>
+          <t>2,02; 19,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 28,45</t>
+          <t>12,58; 27,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,5</t>
+          <t>0,0; 7,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 20,95</t>
+          <t>5,63; 20,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,56</t>
+          <t>1,63; 15,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 25,21</t>
+          <t>12,48; 25,05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,31</t>
+          <t>0,0; 17,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,44</t>
+          <t>0,0; 12,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 17,78</t>
+          <t>4,14; 18,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 18,37</t>
+          <t>3,88; 17,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,32; 26,6</t>
+          <t>9,27; 26,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 13,05</t>
+          <t>1,54; 13,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,27; 25,93</t>
+          <t>14,03; 26,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 15,05</t>
+          <t>3,32; 15,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 19,75</t>
+          <t>6,94; 18,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 9,35</t>
+          <t>1,14; 9,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 20,87</t>
+          <t>12,66; 21,53</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,99</t>
+          <t>4,38; 13,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,49</t>
+          <t>2,0; 9,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 24,15</t>
+          <t>13,71; 23,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,67</t>
+          <t>1,99; 7,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,12; 23,98</t>
+          <t>14,1; 23,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,86</t>
+          <t>3,71; 10,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,19; 28,1</t>
+          <t>21,33; 27,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,32</t>
+          <t>1,31; 5,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,57; 18,56</t>
+          <t>11,78; 19,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,66</t>
+          <t>3,81; 9,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,87; 25,45</t>
+          <t>19,87; 25,28</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39174</t>
+          <t>41396</t>
         </is>
       </c>
     </row>
@@ -1650,57 +1650,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1947; 10968</t>
+          <t>2011; 10992</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1679; 9246</t>
+          <t>2381; 9442</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8790; 18982</t>
+          <t>8696; 19180</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5274</t>
+          <t>0; 5365</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8884; 23240</t>
+          <t>8663; 22596</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2268; 11919</t>
+          <t>2265; 12789</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20814; 31247</t>
+          <t>22307; 33410</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5329</t>
+          <t>0; 5424</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12808; 29685</t>
+          <t>13221; 29335</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5846; 18672</t>
+          <t>5789; 18776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31681; 46955</t>
+          <t>33835; 49839</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22971</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>32841</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1127; 10120</t>
+          <t>1103; 9525</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,47 +1868,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4413; 12247</t>
+          <t>4560; 12815</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5365</t>
+          <t>0; 5108</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7699; 22504</t>
+          <t>8620; 21651</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1206; 10401</t>
+          <t>1203; 10581</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17749; 29485</t>
+          <t>18787; 30686</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5438</t>
+          <t>0; 6278</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11276; 28160</t>
+          <t>12039; 28985</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1191; 9855</t>
+          <t>1192; 9656</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23970; 37976</t>
+          <t>24874; 40270</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>17015</t>
         </is>
       </c>
     </row>
@@ -2066,57 +2066,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4651</t>
+          <t>0; 5592</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4829</t>
+          <t>0; 3995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1475; 8537</t>
+          <t>1555; 9197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5616</t>
+          <t>0; 6382</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3341; 14163</t>
+          <t>4103; 15273</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1031; 11073</t>
+          <t>1040; 9800</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7309; 16589</t>
+          <t>8163; 17759</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5786</t>
+          <t>0; 4856</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4887; 16727</t>
+          <t>4495; 16328</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1260; 11646</t>
+          <t>1218; 11281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10552; 21134</t>
+          <t>11811; 23699</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24028</t>
+          <t>26332</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4231</t>
+          <t>0; 4020</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5780</t>
+          <t>0; 4867</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2284,47 +2284,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1667; 7686</t>
+          <t>1844; 8343</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2815; 13225</t>
+          <t>2796; 12944</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8081; 20823</t>
+          <t>7258; 21080</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1231; 10288</t>
+          <t>1211; 10836</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14882; 27033</t>
+          <t>15835; 29563</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3168; 14308</t>
+          <t>3157; 14639</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8297; 23363</t>
+          <t>8216; 22080</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1241; 10130</t>
+          <t>1238; 10313</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17990; 30779</t>
+          <t>19928; 33887</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>80752</t>
+          <t>86848</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>117584</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6158; 20445</t>
+          <t>6405; 19858</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2442; 11524</t>
+          <t>2430; 11702</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22056; 37927</t>
+          <t>23183; 40028</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4420; 17722</t>
+          <t>4599; 17041</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39457; 67023</t>
+          <t>39427; 66518</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10177; 29027</t>
+          <t>9908; 28902</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>69568; 92229</t>
+          <t>76206; 98127</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5392; 19014</t>
+          <t>4675; 18213</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49252; 79016</t>
+          <t>50132; 80908</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14368; 33654</t>
+          <t>14812; 35603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96424; 123491</t>
+          <t>104581; 133084</t>
         </is>
       </c>
     </row>
